--- a/excel/RPT_3_2026-02-18_normalized.xlsx
+++ b/excel/RPT_3_2026-02-18_normalized.xlsx
@@ -18595,7 +18595,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-03-19T18:51:36</t>
+          <t>2026-03-19T20:38:29</t>
         </is>
       </c>
     </row>
